--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.01499906001483</v>
+        <v>5.68993734725241</v>
       </c>
       <c r="D2" t="n">
-        <v>34.60954407742719</v>
+        <v>5.624050912581918</v>
       </c>
       <c r="E2" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F2" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>13.24210339273767</v>
+        <v>2.151841801319871</v>
       </c>
       <c r="D3" t="n">
-        <v>13.21457964658968</v>
+        <v>2.147369192570823</v>
       </c>
       <c r="E3" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F3" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>44.35810714247983</v>
+        <v>7.208192410652972</v>
       </c>
       <c r="D4" t="n">
-        <v>44.93641527014651</v>
+        <v>7.302167481398809</v>
       </c>
       <c r="E4" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F4" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.148312809313092</v>
+        <v>0.6741008315133774</v>
       </c>
       <c r="D5" t="n">
-        <v>4.459568544919303</v>
+        <v>0.7246798885493867</v>
       </c>
       <c r="E5" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F5" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>8.91763300322709</v>
+        <v>1.449115363024402</v>
       </c>
       <c r="D6" t="n">
-        <v>8.339278594510404</v>
+        <v>1.355132771607941</v>
       </c>
       <c r="E6" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F6" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.71135816346833</v>
+        <v>6.615595701563604</v>
       </c>
       <c r="D7" t="n">
-        <v>40.11463768891026</v>
+        <v>6.518628624447917</v>
       </c>
       <c r="E7" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F7" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>12.55163914880647</v>
+        <v>2.039641361681051</v>
       </c>
       <c r="D8" t="n">
-        <v>13.02850344730152</v>
+        <v>2.117131810186497</v>
       </c>
       <c r="E8" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F8" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>35.08689958755035</v>
+        <v>5.701621182976932</v>
       </c>
       <c r="D9" t="n">
-        <v>35.60335915086378</v>
+        <v>5.785545862015365</v>
       </c>
       <c r="E9" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F9" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>46.81435137056081</v>
+        <v>7.607332097716133</v>
       </c>
       <c r="D10" t="n">
-        <v>47.22297831365322</v>
+        <v>7.673733975968648</v>
       </c>
       <c r="E10" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F10" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>74.04122976764785</v>
+        <v>12.03169983724278</v>
       </c>
       <c r="D11" t="n">
-        <v>73.50788260917479</v>
+        <v>11.9450309239909</v>
       </c>
       <c r="E11" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F11" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>67.28767337519464</v>
+        <v>10.93424692346913</v>
       </c>
       <c r="D12" t="n">
-        <v>66.79811226841097</v>
+        <v>10.85469324361678</v>
       </c>
       <c r="E12" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F12" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>66.15272217930087</v>
+        <v>10.74981735413639</v>
       </c>
       <c r="D13" t="n">
-        <v>65.71018606556397</v>
+        <v>10.67790523565415</v>
       </c>
       <c r="E13" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F13" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>48.43994088009753</v>
+        <v>7.871490393015849</v>
       </c>
       <c r="D14" t="n">
-        <v>48.38969235091373</v>
+        <v>7.863325007023482</v>
       </c>
       <c r="E14" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F14" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>57.34370452019773</v>
+        <v>9.31835198453213</v>
       </c>
       <c r="D15" t="n">
-        <v>57.07090697254389</v>
+        <v>9.274022383038382</v>
       </c>
       <c r="E15" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F15" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>61.88294667434911</v>
+        <v>10.05597883458173</v>
       </c>
       <c r="D16" t="n">
-        <v>61.56003591581315</v>
+        <v>10.00350583631964</v>
       </c>
       <c r="E16" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F16" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>56.81582445294036</v>
+        <v>9.232571473602809</v>
       </c>
       <c r="D17" t="n">
-        <v>56.79789598569152</v>
+        <v>9.229658097674871</v>
       </c>
       <c r="E17" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F17" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>64.06866303549809</v>
+        <v>10.41115774326844</v>
       </c>
       <c r="D18" t="n">
-        <v>63.8886509487808</v>
+        <v>10.38190577917688</v>
       </c>
       <c r="E18" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F18" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>103.7750042380424</v>
+        <v>16.86343818868189</v>
       </c>
       <c r="D19" t="n">
-        <v>103.775058875374</v>
+        <v>16.86344706724828</v>
       </c>
       <c r="E19" t="n">
-        <v>25.16021662687282</v>
+        <v>4.088535201866833</v>
       </c>
       <c r="F19" t="n">
-        <v>25.05212877094808</v>
+        <v>4.070970925279063</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
